--- a/hmwebsite/chords/resources/data.xlsx
+++ b/hmwebsite/chords/resources/data.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Dropbox\Html Tools\hmwebsite\hmwebsite\chords\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\git\hmon.ir\hmwebsite\chords\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D633FD4C-15D2-43A8-903D-03237D72A0B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A193A20A-3988-4AAC-985D-EA76E4F6C514}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-315" windowWidth="29040" windowHeight="17640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="items" sheetId="1" r:id="rId1"/>
@@ -247,12 +247,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="1" tint="0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="9">
@@ -347,22 +353,81 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="7">
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -376,16 +441,16 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{91365E13-2B03-42F7-AE33-A38BD1C73E8F}" name="Table1" displayName="Table1" ref="B1:F25" totalsRowShown="0">
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:E9">
-    <sortCondition ref="C7:C9"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{91365E13-2B03-42F7-AE33-A38BD1C73E8F}" name="Table1" displayName="Table1" ref="A1:E25" totalsRowShown="0" headerRowDxfId="1" dataDxfId="0">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D9">
+    <sortCondition ref="B7:B9"/>
   </sortState>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{3D053E9F-E76F-4AA8-9907-A5D0C5572475}" name="category"/>
-    <tableColumn id="2" xr3:uid="{FE16CA46-A911-4065-9678-BA421DED1555}" name="sortOrder"/>
-    <tableColumn id="3" xr3:uid="{F0E06C2E-5C7A-41B3-85F5-42CB7DE704FF}" name="name"/>
-    <tableColumn id="4" xr3:uid="{D1CEE981-B5D8-4C6E-859D-8E8D7A7B1BEE}" name="path"/>
-    <tableColumn id="5" xr3:uid="{6EC52A06-1682-4082-8D87-A73474C7D0F4}" name="title"/>
+    <tableColumn id="1" xr3:uid="{3D053E9F-E76F-4AA8-9907-A5D0C5572475}" name="category" dataDxfId="6"/>
+    <tableColumn id="2" xr3:uid="{FE16CA46-A911-4065-9678-BA421DED1555}" name="sortOrder" dataDxfId="5"/>
+    <tableColumn id="3" xr3:uid="{F0E06C2E-5C7A-41B3-85F5-42CB7DE704FF}" name="name" dataDxfId="4"/>
+    <tableColumn id="4" xr3:uid="{D1CEE981-B5D8-4C6E-859D-8E8D7A7B1BEE}" name="path" dataDxfId="3"/>
+    <tableColumn id="5" xr3:uid="{6EC52A06-1682-4082-8D87-A73474C7D0F4}" name="title" dataDxfId="2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -654,437 +719,439 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B1:F25"/>
+  <dimension ref="A1:E25"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="10.7109375" customWidth="1"/>
-    <col min="3" max="3" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="36.42578125" customWidth="1"/>
-    <col min="6" max="6" width="29.5703125" customWidth="1"/>
+    <col min="1" max="1" width="10.7109375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="9.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.140625" style="1"/>
+    <col min="4" max="4" width="36.42578125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="29.5703125" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B1" t="s">
+    <row r="1" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C1" t="s">
+      <c r="B1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="C1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E1" t="s">
+      <c r="D1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="F1" t="s">
+      <c r="E1" s="2" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="2" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B2" s="1" t="s">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="C2" s="2">
+      <c r="B2" s="4">
         <v>1</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="C2" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="D2" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="E2" s="5" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="3" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B3" s="4" t="s">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="C3" s="5">
+      <c r="B3" s="7">
         <v>2</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="C3" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="D3" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="E3" s="8" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="4" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B4" s="4" t="s">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="C4" s="5">
+      <c r="B4" s="7">
         <v>3</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="C4" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="D4" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="F4" s="6" t="s">
+      <c r="E4" s="8" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="5" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="7" t="s">
+    <row r="5" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="C5" s="8">
+      <c r="B5" s="10">
         <v>4</v>
       </c>
-      <c r="D5" s="8" t="s">
+      <c r="C5" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="E5" s="8" t="s">
+      <c r="D5" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="F5" s="9" t="s">
+      <c r="E5" s="11" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="6" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B6" s="1" t="s">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C6" s="2">
+      <c r="B6" s="4">
         <v>1</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="C6" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="D6" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="F6" s="3" t="s">
+      <c r="E6" s="5" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="7" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B7" s="4" t="s">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C7" s="5">
+      <c r="B7" s="7">
         <v>2</v>
       </c>
-      <c r="D7" s="5" t="s">
+      <c r="C7" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="E7" s="5" t="s">
+      <c r="D7" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="F7" s="6" t="s">
+      <c r="E7" s="8" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="8" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B8" s="4" t="s">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C8" s="5">
+      <c r="B8" s="7">
         <v>3</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="C8" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="E8" s="5" t="s">
+      <c r="D8" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="F8" s="6" t="s">
+      <c r="E8" s="8" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="9" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B9" s="4" t="s">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C9" s="5">
+      <c r="B9" s="7">
         <v>4</v>
       </c>
-      <c r="D9" s="5" t="s">
+      <c r="C9" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="E9" s="5" t="s">
+      <c r="D9" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F9" s="6" t="s">
+      <c r="E9" s="8" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="10" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="7" t="s">
+    <row r="10" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="C10" s="8">
+      <c r="B10" s="10">
         <v>5</v>
       </c>
-      <c r="D10" s="8" t="s">
+      <c r="C10" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="E10" s="5" t="s">
+      <c r="D10" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="F10" s="9" t="s">
+      <c r="E10" s="11" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="11" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B11" s="1" t="s">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C11" s="2">
+      <c r="B11" s="4">
         <v>1</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="C11" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="E11" s="2" t="s">
+      <c r="D11" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="F11" s="3" t="s">
+      <c r="E11" s="5" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="12" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B12" s="4" t="s">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="C12" s="5">
+      <c r="B12" s="7">
         <v>2</v>
       </c>
-      <c r="D12" s="5" t="s">
+      <c r="C12" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="E12" s="5" t="s">
+      <c r="D12" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="F12" s="6" t="s">
+      <c r="E12" s="8" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="13" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B13" s="4" t="s">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="C13" s="5">
+      <c r="B13" s="7">
         <v>3</v>
       </c>
-      <c r="D13" s="5" t="s">
+      <c r="C13" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="E13" s="5" t="s">
+      <c r="D13" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="F13" s="6" t="s">
+      <c r="E13" s="8" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="14" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B14" s="4" t="s">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="C14" s="5">
+      <c r="B14" s="7">
         <v>4</v>
       </c>
-      <c r="D14" s="5" t="s">
+      <c r="C14" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="E14" s="5" t="s">
+      <c r="D14" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="F14" s="6" t="s">
+      <c r="E14" s="8" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="15" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B15" s="4" t="s">
+    <row r="15" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="C15" s="5">
+      <c r="B15" s="7">
         <v>5</v>
       </c>
-      <c r="D15" s="5" t="s">
+      <c r="C15" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="E15" s="5" t="s">
+      <c r="D15" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="F15" s="6" t="s">
+      <c r="E15" s="8" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="16" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B16" s="1" t="s">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="C16" s="2">
+      <c r="B16" s="4">
         <v>1</v>
       </c>
-      <c r="D16" s="2" t="s">
+      <c r="C16" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="E16" s="2" t="s">
+      <c r="D16" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="F16" s="3" t="s">
+      <c r="E16" s="5" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B17" s="4" t="s">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="C17" s="5">
+      <c r="B17" s="7">
         <v>2</v>
       </c>
-      <c r="D17" s="5" t="s">
+      <c r="C17" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="E17" s="5" t="s">
+      <c r="D17" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="F17" s="6" t="s">
+      <c r="E17" s="8" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="18" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B18" s="4" t="s">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="C18" s="5">
+      <c r="B18" s="7">
         <v>3</v>
       </c>
-      <c r="D18" s="5" t="s">
+      <c r="C18" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="E18" s="5" t="s">
+      <c r="D18" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="F18" s="6" t="s">
+      <c r="E18" s="8" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="19" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B19" s="4" t="s">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="C19" s="5">
+      <c r="B19" s="7">
         <v>4</v>
       </c>
-      <c r="D19" s="5" t="s">
+      <c r="C19" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="E19" s="5" t="s">
+      <c r="D19" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="F19" s="6" t="s">
+      <c r="E19" s="8" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="20" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="7" t="s">
+    <row r="20" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="C20" s="8">
+      <c r="B20" s="10">
         <v>5</v>
       </c>
-      <c r="D20" s="5" t="s">
+      <c r="C20" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="E20" s="5" t="s">
+      <c r="D20" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="F20" s="6" t="s">
+      <c r="E20" s="8" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="21" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B21" s="1" t="s">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="C21" s="2">
+      <c r="B21" s="4">
         <v>1</v>
       </c>
-      <c r="D21" s="2" t="s">
+      <c r="C21" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="E21" s="2" t="s">
+      <c r="D21" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="F21" s="3" t="s">
+      <c r="E21" s="5" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="22" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B22" s="4" t="s">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="C22" s="5">
+      <c r="B22" s="7">
         <v>2</v>
       </c>
-      <c r="D22" s="5" t="s">
+      <c r="C22" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="E22" s="5" t="s">
+      <c r="D22" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="F22" s="6" t="s">
+      <c r="E22" s="8" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="23" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B23" s="4" t="s">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="C23" s="5">
+      <c r="B23" s="7">
         <v>3</v>
       </c>
-      <c r="D23" s="5" t="s">
+      <c r="C23" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="E23" s="5" t="s">
+      <c r="D23" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="F23" s="6" t="s">
+      <c r="E23" s="8" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="24" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B24" s="4" t="s">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="C24" s="5">
+      <c r="B24" s="7">
         <v>4</v>
       </c>
-      <c r="D24" s="5" t="s">
+      <c r="C24" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="E24" s="5" t="s">
+      <c r="D24" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="F24" s="6" t="s">
+      <c r="E24" s="8" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="25" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B25" s="7" t="s">
+    <row r="25" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="C25" s="8">
+      <c r="B25" s="10">
         <v>5</v>
       </c>
-      <c r="D25" s="8" t="s">
+      <c r="C25" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="E25" s="8" t="s">
+      <c r="D25" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="F25" s="9" t="s">
+      <c r="E25" s="11" t="s">
         <v>55</v>
       </c>
     </row>

--- a/hmwebsite/chords/resources/data.xlsx
+++ b/hmwebsite/chords/resources/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\git\hmon.ir\hmwebsite\chords\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A193A20A-3988-4AAC-985D-EA76E4F6C514}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3DB1100-E3C1-42B0-961C-DB1A83881303}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-315" windowWidth="29040" windowHeight="17640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -441,16 +441,16 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{91365E13-2B03-42F7-AE33-A38BD1C73E8F}" name="Table1" displayName="Table1" ref="A1:E25" totalsRowShown="0" headerRowDxfId="1" dataDxfId="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{91365E13-2B03-42F7-AE33-A38BD1C73E8F}" name="Table1" displayName="Table1" ref="A1:E25" totalsRowShown="0" headerRowDxfId="6" dataDxfId="5">
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D9">
     <sortCondition ref="B7:B9"/>
   </sortState>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{3D053E9F-E76F-4AA8-9907-A5D0C5572475}" name="category" dataDxfId="6"/>
-    <tableColumn id="2" xr3:uid="{FE16CA46-A911-4065-9678-BA421DED1555}" name="sortOrder" dataDxfId="5"/>
-    <tableColumn id="3" xr3:uid="{F0E06C2E-5C7A-41B3-85F5-42CB7DE704FF}" name="name" dataDxfId="4"/>
-    <tableColumn id="4" xr3:uid="{D1CEE981-B5D8-4C6E-859D-8E8D7A7B1BEE}" name="path" dataDxfId="3"/>
-    <tableColumn id="5" xr3:uid="{6EC52A06-1682-4082-8D87-A73474C7D0F4}" name="title" dataDxfId="2"/>
+    <tableColumn id="1" xr3:uid="{3D053E9F-E76F-4AA8-9907-A5D0C5572475}" name="category" dataDxfId="4"/>
+    <tableColumn id="2" xr3:uid="{FE16CA46-A911-4065-9678-BA421DED1555}" name="sortOrder" dataDxfId="3"/>
+    <tableColumn id="3" xr3:uid="{F0E06C2E-5C7A-41B3-85F5-42CB7DE704FF}" name="name" dataDxfId="2"/>
+    <tableColumn id="4" xr3:uid="{D1CEE981-B5D8-4C6E-859D-8E8D7A7B1BEE}" name="path" dataDxfId="1"/>
+    <tableColumn id="5" xr3:uid="{6EC52A06-1682-4082-8D87-A73474C7D0F4}" name="title" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
